--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_items_type[道具类型].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_items_type[道具类型].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="ItemsType" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
   <si>
     <t>id</t>
   </si>
@@ -87,6 +87,9 @@
   </si>
   <si>
     <t>鼻环</t>
+  </si>
+  <si>
+    <t>戒指</t>
   </si>
   <si>
     <t>ui_equip_1</t>
@@ -1060,7 +1063,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D70"/>
+  <dimension ref="A1:D71"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28.625" customWidth="1"/>
@@ -1184,19 +1187,32 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9">
+        <v>6</v>
+      </c>
+      <c r="D9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10">
         <v>10</v>
       </c>
-      <c r="B9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9">
+      <c r="B10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10">
         <v>10</v>
       </c>
-      <c r="D9" t="s">
-        <v>21</v>
+      <c r="D10" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1"/>
     <row r="21" ht="15" customHeight="1"/>
     <row r="22" ht="15" customHeight="1"/>
     <row r="23" ht="15" customHeight="1"/>
@@ -1207,7 +1223,7 @@
     <row r="28" ht="15" customHeight="1"/>
     <row r="29" ht="15" customHeight="1"/>
     <row r="30" ht="15" customHeight="1"/>
-    <row r="62" ht="12" customHeight="1"/>
+    <row r="31" ht="15" customHeight="1"/>
     <row r="63" ht="12" customHeight="1"/>
     <row r="64" ht="12" customHeight="1"/>
     <row r="65" ht="12" customHeight="1"/>
@@ -1216,6 +1232,7 @@
     <row r="68" ht="12" customHeight="1"/>
     <row r="69" ht="12" customHeight="1"/>
     <row r="70" ht="12" customHeight="1"/>
+    <row r="71" ht="12" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_items_type[道具类型].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_items_type[道具类型].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="ItemsType" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
   <si>
     <t>id</t>
   </si>
@@ -96,6 +96,9 @@
   </si>
   <si>
     <t>武器</t>
+  </si>
+  <si>
+    <t>肖像</t>
   </si>
 </sst>
 </file>
@@ -1213,6 +1216,20 @@
         <v>22</v>
       </c>
     </row>
+    <row r="11" spans="1:4">
+      <c r="A11">
+        <v>101</v>
+      </c>
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11">
+        <v>101</v>
+      </c>
+      <c r="D11" t="s">
+        <v>23</v>
+      </c>
+    </row>
     <row r="21" ht="15" customHeight="1"/>
     <row r="22" ht="15" customHeight="1"/>
     <row r="23" ht="15" customHeight="1"/>
